--- a/光伏配储项目/电价数据/2026/基地站.xlsx
+++ b/光伏配储项目/电价数据/2026/基地站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.508</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.83549</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57952</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.69217</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5723200000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.58063</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43566</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38325</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38415</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42232</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44219</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.24625</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.15757</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.14102</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.17969</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.18619</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.25496</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.25265</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.12824</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.05631</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.1404</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01106</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.13716</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.20729</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23718</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.11627</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.10324</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.03442</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.19426</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.10881</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.26164</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.06102</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.16289</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.9343899999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.80914</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.52061</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.39995</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.47556</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9471499999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.60263</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.40463</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.7773300000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42531</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.82826</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.65908</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.66725</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.6672100000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.73365</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7172799999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52118</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47941</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42224</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.78776</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.75419</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.79201</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.6571</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.80452</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53612</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5225599999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50625</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.54334</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49791</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41479</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47238</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.39186</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42096</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6087100000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72373</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43244</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.51825</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.57692</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.22752</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26363</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.14832</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.56945</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.58899</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.88815</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.51166</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.47442</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>1.1387</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.59003</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.6294500000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.41855</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.71834</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.47195</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.32822</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.34371</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.12394</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.3461</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.08052</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.6142</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.38277</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.79401</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.47929</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.57759</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.56157</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.59853</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.61467</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.44322</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.9282699999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7924</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.96166</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43469</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33351</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51539</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48534</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47329</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44392</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.23658</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6960299999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5330499999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.6170099999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5465399999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.5580700000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.58392</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>1.02629</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.5323</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.43356</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.27887</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33282</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.46178</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.46401</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.60454</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.49559</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.79514</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.47712</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.43878</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.00276</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.44337</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.07074</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.60337</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.35251</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.73985</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.7905599999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.5806699999999999</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.7464400000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.52942</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.63225</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.5325700000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.51864</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5126000000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.53025</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.5088</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.46683</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34313</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.48272</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.46156</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46646</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30204</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.23553</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.28196</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.27183</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.14669</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.07554</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.20694</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.13729</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6054299999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.81198</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.18215</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.46712</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.19515</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.98449</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.27638</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.6335299999999999</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.5932799999999999</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.88727</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.41104</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.44422</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.16388</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.22849</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.14346</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20415</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.08635</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19314</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.2172</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.23235</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.8003400000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.02526</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.14666</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.50238</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.28189</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30266</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29536</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.02221</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.01671</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.02094</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03225</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.02793</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.02536</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.03479</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.02444</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.23546</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03165</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.03816</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.04597</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.0225</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.13212</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.08727</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28027</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34978</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65371</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09570000000000001</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03198</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04658</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04508</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04317</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04833</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09395000000000001</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00618</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04293</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04228</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.03981000000000001</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04227</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0402</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04345</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.13465</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28669</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.2863</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26592</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33655</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31242</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28889</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16828</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15412</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17181</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14842</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16015</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15939</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23745</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21481</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22464</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27304</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28075</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.23691</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.27327</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4601</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41194</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.16499</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27448</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.28219</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.49808</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79213</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6150599999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39133</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.48739</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.77093</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.8992899999999999</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.47942</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.8978200000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8743300000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.28131</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8847</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.61636</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.17876</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33071</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.02796</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5389400000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8064199999999999</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53037</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7898500000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87861</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88198</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5076499999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41853</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22563</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8793800000000001</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63964</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5429299999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50268</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45256</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34834</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58675</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59624</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58827</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66116</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.19741</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50822</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.66671</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8539600000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.57985</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.5598</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.34054</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.6733899999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.85911</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.50445</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.23511</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.23136</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.25808</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35302</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95682</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47749</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.48655</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41224</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38769</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.8139</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.42884</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.25413</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>1.16486</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.14734</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.41314</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.8613500000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19695</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27173</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.21452</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.23786</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.10565</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.20707</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.81012</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.48526</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27159</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.46926</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59678</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8720800000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.30553</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.11948</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70368</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79545</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64985</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58374</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42353</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50056</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.50359</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.66185</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>1.17967</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.87079</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.11296</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.93787</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.11921</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.4151</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.42176</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.17334</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.16686</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.23865</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.9473200000000001</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.47791</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.44125</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.40646</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.41316</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.10217</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.26632</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.08043</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.82684</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>1.11725</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.05135</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.9936699999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.82713</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.8083400000000001</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>1.14337</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>1.26409</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>1.20853</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.47906</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.17235</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.14957</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.45302</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.57365</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.35853</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.51077</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32473</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42207</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39132</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.38804</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.64773</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.24539</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.43881</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.59782</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.5488500000000001</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.27638</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13672</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26101</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13837</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27268</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13742</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.1282</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10621</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10568</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.16522</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13422</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14611</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40022</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39775</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44031</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43931</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44423</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44429</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34936</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5424500000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46871</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37958</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30528</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.24453</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25357</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24145</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23679</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26542</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.25116</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30162</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22872</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.40735</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.67904</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.93974</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.4364</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.31189</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.9414400000000001</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.46791</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.75919</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.04222</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.30968</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.25127</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.1536</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49989</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36026</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41865</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38049</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.29305</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.76022</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.1437</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.05296</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.20146</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.21264</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.12834</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.1968</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.07688</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.06956</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.13702</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.93511</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.46703</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24657</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.8724</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.54015</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.5236499999999999</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.48948</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.06919</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.05225</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.08569</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.09905</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.09415</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.07127</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.09574</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.15134</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.12882</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.1069</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.21026</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.12412</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.12584</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.13358</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.14169</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.1043</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.17597</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.13622</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.26293</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.11966</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.12806</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.12193</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.24528</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.2014</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.51836</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.15158</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.18914</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.46082</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.0616</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34041</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29474</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.87346</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.50991</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.8339299999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.46758</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5030899999999999</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.26866</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56335</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42922</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65197</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83111</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47187</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45944</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34478</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.45528</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.54552</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.6076</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.83002</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.8461900000000001</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.24283</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.27616</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.21981</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.63966</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.5307000000000001</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.8443999999999999</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.8445900000000001</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.6045900000000001</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.53438</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.4759</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.12607</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.73115</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.61334</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.28247</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.24904</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.30974</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.28442</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.27291</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.17657</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.34835</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.2963</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.31098</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.26313</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.91365</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.31671</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.9623400000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.48476</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>1.06828</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.87986</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.05762</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.75054</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42985</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41878</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48037</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.61005</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5521900000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.29059</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41649</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39979</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50059</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45062</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.84597</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.16463</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.10107</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.21149</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.17901</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.26256</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.53551</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.40969</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.00877</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.84915</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.1784</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.28865</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.27875</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.29337</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.29107</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.21371</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.23291</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.83216</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.23501</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.16939</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.1143</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.9598099999999999</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.90079</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.86429</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.16413</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.8520599999999999</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.27037</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37441</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.51405</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.43482</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48118</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.64986</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.89067</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.03122</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.9726</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.84914</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.74758</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.57428</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.90573</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.84124</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.69233</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6155</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.5624400000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.56059</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.46016</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4781</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.4715</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.67237</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.48054</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43681</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42658</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44841</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45776</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38856</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.38373</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.8696900000000001</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.8479800000000001</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.8313700000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.70498</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.3159</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.67744</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.6665</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.37152</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.18547</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.48524</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.06542</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5317999999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.03794</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5425099999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.60895</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.44421</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.41026</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.52404</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.5678300000000001</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.52643</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46806</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.44967</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.59765</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5805399999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.70743</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40609</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36414</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22698</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22599</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22022</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24205</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.04623</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.11998</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.21831</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.13907</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25073</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.13486</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>-0.01407</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21325</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22638</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13296</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21121</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.26133</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.4124</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3517</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31667</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30683</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22459</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21307</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.14941</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17798</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.01713</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.13082</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.0451</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.17874</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.07640000000000001</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.16985</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.03002</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.01899</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.18132</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04115</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.08692</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16579</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21018</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24535</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24782</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.24972</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26112</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26598</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25535</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30203</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27994</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.2632</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2719</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25011</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19312</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.04809</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29745</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.009779999999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.05149</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24087</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22162</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.21035</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.13555</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26129</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24274</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.21968</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20279</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18583</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21243</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16452</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.18156</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.2198</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21955</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24081</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.22769</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21058</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2586</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22362</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26534</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26753</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.23203</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.17959</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.05699</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.48602</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.64652</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.49216</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17982</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20812</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09422</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.03356</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.02212</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.02719</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.1967</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.02683</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.12272</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.00604</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.12325</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.03206000000000001</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.09877</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.08143</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.005650000000000001</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.08015</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.03933</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.44163</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.26758</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.14548</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.4352</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.37715</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.25605</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.42228</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32411</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33172</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.07031</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.86051</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.71013</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5833400000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.55357</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44179</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.49147</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.43339</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>1.06926</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.50895</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.34541</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.25818</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.34847</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.25766</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.25227</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.26915</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.28732</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.8427</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.59124</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.59905</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.6716</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13183</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26659</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.58638</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.12988</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.50717</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.01799</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.29966</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.55729</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47012</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33014</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.25604</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.43089</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.00938</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.2351</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.61153</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.22843</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35773</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.7855</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.42329</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.93647</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.19955</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.22209</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.2694</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.33618</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.31932</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.38915</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.40167</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.37956</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.42245</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.2991</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.23017</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.5221</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.5791</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.23377</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.33678</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.1192</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.89261</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.89708</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.96017</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.84589</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6868099999999999</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.6387</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.42816</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.52185</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.55853</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.6159600000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.53096</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.18452</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.16247</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.44474</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.24107</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.44368</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.42643</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.47744</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.40335</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.5780599999999999</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.39381</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.17323</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.48536</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.48555</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.9204</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.13367</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.23398</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.23614</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.34472</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.25701</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.34832</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.32998</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.36196</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.36221</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.28699</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.36342</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.34405</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.39141</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.46437</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.7254299999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.54796</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.33534</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.42594</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.42046</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.48081</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.57176</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48622</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.69457</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.67337</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.00833</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9487599999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7159800000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.71777</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37508</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8932</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.47054</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.11256</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>1.0425</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>1.06882</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.24267</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.41652</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.40029</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.97312</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.8120599999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.7036</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.49818</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.54786</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.32527</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.00718</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.02826</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.81184</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.27659</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.12185</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.42166</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.27006</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.26937</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.33604</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.26892</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.6004400000000001</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.36204</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.8714</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.70427</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.352</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.96834</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.8466900000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.33401</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>1.06698</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.16247</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.39076</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.17845</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.17746</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.26326</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.15894</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.16952</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.26803</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.24018</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.2932</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.4897</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.26282</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.39065</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.2283</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.20874</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.23881</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.29214</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.31536</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.2959</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.44631</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.83863</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.73393</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.66543</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.6323799999999999</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37544</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.76016</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.45858</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.4462</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.18886</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.17642</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5444199999999999</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.8298</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.68513</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.86897</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.89075</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.8335199999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.17002</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.9530299999999999</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.17545</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.09023</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.8300700000000001</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.82399</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9799800000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.9591799999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.79289</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.06577</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.67689</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.9740800000000001</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.01613</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.06948</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.20706</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.10317</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.26067</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.81789</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.02457</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.85178</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7886599999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.55335</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.6372100000000001</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.59436</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.78162</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.6843400000000001</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42059</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.43291</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.48517</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.27644</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.23373</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.46179</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.25163</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.17434</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36416</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5635399999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.22289</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.23756</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.07747</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.22426</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.07851000000000001</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.10841</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>-0.01194</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.13604</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.24981</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.23624</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.25557</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5898</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.21686</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.22116</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.00595</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.98699</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.21928</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.6013200000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.21265</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.88214</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.02676</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.03157</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20989</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.08957999999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.26725</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.10154</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.23994</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24152</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.48862</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.91107</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.8338</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6731699999999999</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.65216</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6332899999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.81992</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.90459</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.88042</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.70502</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.58645</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.5837</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.45125</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.83414</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.63476</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.44638</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.7374299999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.86036</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.7397899999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.45718</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38407</v>
       </c>
     </row>
   </sheetData>
